--- a/config/generated/templates/UniverseEvidence.xlsx
+++ b/config/generated/templates/UniverseEvidence.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="83">
   <si>
     <t>@table</t>
   </si>
@@ -134,7 +134,7 @@
     <t>UniverseContentAudit</t>
   </si>
   <si>
-    <t>ecab773269fe3ff3</t>
+    <t>aaaebf829c6c5b64</t>
   </si>
   <si>
     <t>content_stable_key</t>
@@ -173,70 +173,73 @@
     <t>list&lt;ref&lt;UniverseSourceRecord.id&gt;&gt;</t>
   </si>
   <si>
+    <t>optional&lt;list&lt;string&gt;&gt;</t>
+  </si>
+  <si>
+    <t>optional&lt;string&gt;</t>
+  </si>
+  <si>
+    <t>length=1..200</t>
+  </si>
+  <si>
+    <t>parser=split;separator=|;length=1..64</t>
+  </si>
+  <si>
+    <t>parser=split;separator=|;length=0..64</t>
+  </si>
+  <si>
+    <t>UniverseCoverage</t>
+  </si>
+  <si>
+    <t>48259865a9f33b6c</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>accounted</t>
+  </si>
+  <si>
+    <t>data_ready</t>
+  </si>
+  <si>
+    <t>coverage_percent_decimal</t>
+  </si>
+  <si>
+    <t>length=1..160</t>
+  </si>
+  <si>
+    <t>range=0..1000000</t>
+  </si>
+  <si>
+    <t>UniverseReviewFixture</t>
+  </si>
+  <si>
+    <t>008bd7df6bd5ef86</t>
+  </si>
+  <si>
+    <t>mechanic_family</t>
+  </si>
+  <si>
+    <t>input_stable_keys</t>
+  </si>
+  <si>
+    <t>initial_state_json</t>
+  </si>
+  <si>
+    <t>commands_json</t>
+  </si>
+  <si>
+    <t>expected_facts_json</t>
+  </si>
+  <si>
+    <t>quality_floor</t>
+  </si>
+  <si>
     <t>list&lt;string&gt;</t>
-  </si>
-  <si>
-    <t>optional&lt;string&gt;</t>
-  </si>
-  <si>
-    <t>length=1..200</t>
-  </si>
-  <si>
-    <t>parser=split;separator=|;length=1..64</t>
-  </si>
-  <si>
-    <t>parser=split;separator=|;length=0..64</t>
-  </si>
-  <si>
-    <t>UniverseCoverage</t>
-  </si>
-  <si>
-    <t>48259865a9f33b6c</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>accounted</t>
-  </si>
-  <si>
-    <t>data_ready</t>
-  </si>
-  <si>
-    <t>coverage_percent_decimal</t>
-  </si>
-  <si>
-    <t>length=1..160</t>
-  </si>
-  <si>
-    <t>range=0..1000000</t>
-  </si>
-  <si>
-    <t>UniverseReviewFixture</t>
-  </si>
-  <si>
-    <t>008bd7df6bd5ef86</t>
-  </si>
-  <si>
-    <t>mechanic_family</t>
-  </si>
-  <si>
-    <t>input_stable_keys</t>
-  </si>
-  <si>
-    <t>initial_state_json</t>
-  </si>
-  <si>
-    <t>commands_json</t>
-  </si>
-  <si>
-    <t>expected_facts_json</t>
-  </si>
-  <si>
-    <t>quality_floor</t>
   </si>
   <si>
     <t>length=2..16000</t>
@@ -974,7 +977,7 @@
     <col min="7" max="8" width="25.7109375" style="5" customWidth="1"/>
     <col min="9" max="9" width="27.7109375" style="5" customWidth="1"/>
     <col min="10" max="10" width="32.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="22.7109375" style="5" customWidth="1"/>
     <col min="12" max="12" width="16.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1563,7 +1566,7 @@
         <v>25</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>25</v>
@@ -1630,13 +1633,13 @@
         <v>54</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5" t="s">
@@ -1687,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -1711,7 +1714,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
@@ -1722,16 +1725,16 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1742,16 +1745,16 @@
         <v>5</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1765,7 +1768,7 @@
         <v>25</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>24</v>
@@ -1805,7 +1808,7 @@
         <v>30</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>64</v>
